--- a/processo_2/synthetic_proposals/PROPOSTA_017/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_017/ficha_pontuacao.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -799,8 +799,16 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Revista Científica Avançada 1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3248-2319</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -867,11 +875,15 @@
           <t>sem teto</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -904,13 +916,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
@@ -946,7 +958,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -969,7 +981,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1038,7 +1050,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1063,7 +1075,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1106,7 +1118,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1129,7 +1141,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1175,17 +1187,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1198,17 +1210,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
@@ -1221,17 +1233,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
@@ -1244,17 +1256,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1267,7 +1279,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1290,17 +1302,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>1.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1313,7 +1325,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1531,7 +1543,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1554,7 +1566,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1600,7 +1612,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1623,7 +1635,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1648,7 +1660,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>49</v>
+        <v>24.5</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1718,13 +1730,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
@@ -1831,7 +1843,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1845,7 +1857,9 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>32.5</v>
+      </c>
       <c r="G68" t="inlineStr"/>
     </row>
   </sheetData>
